--- a/docs/projects/perfect-skin/content/inci/GLACEE-sostav-na-proverku.xlsx
+++ b/docs/projects/perfect-skin/content/inci/GLACEE-sostav-na-proverku.xlsx
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>На официальном сайте glacee.es полного состава нет. Перепишите, пожалуйста, состав с упаковки (или пришлите файл поставщика / фото задней стороны упаковки) в жёлтую колонку.</t>
+          <t>На официальном сайте glacee.es полного состава нет. Лучше всего — пришлите фото задней стороны упаковки каждого средства или файл с составами от поставщика: перепишем и сверим сами. Вписать вручную можно в жёлтые колонки.</t>
         </is>
       </c>
     </row>
